--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1FFB7B-0DEB-41AF-9027-C8B206463360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB17668-B776-4878-BD04-BA7FCDE49ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>StoryID</t>
   </si>
@@ -252,6 +252,14 @@
   </si>
   <si>
     <t>after</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/spring.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -867,8 +875,12 @@
       <c r="E2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="F2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="H2" s="14" t="s">
         <v>30</v>
       </c>
@@ -887,7 +899,9 @@
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
         <v>31</v>
@@ -907,7 +921,9 @@
         <v>11</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
         <v>32</v>

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB17668-B776-4878-BD04-BA7FCDE49ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CA6B95-EF34-4E2C-86A1-0A14ACC51EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>StoryID</t>
   </si>
@@ -262,16 +251,19 @@
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -285,7 +277,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -306,7 +298,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -329,6 +321,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -415,8 +415,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -432,9 +430,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -712,24 +712,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -742,36 +743,39 @@
       <c r="D1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="16" t="s">
         <v>20</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -791,25 +795,26 @@
       <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="2"/>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="12"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="12"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="12"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -822,14 +827,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -866,7 +871,7 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -881,7 +886,7 @@
       <c r="G2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1054,12 +1059,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="14"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
@@ -1071,17 +1076,17 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="14"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CA6B95-EF34-4E2C-86A1-0A14ACC51EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D966527-60F2-4609-9F54-01AB18BB7D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -244,15 +244,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/clinic/spring.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_04.png</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
         <v>20</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>21</v>
@@ -881,10 +881,10 @@
         <v>36</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>30</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -927,7 +927,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D966527-60F2-4609-9F54-01AB18BB7D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B2CC11-A98F-4F0D-965E-B7E42BA6168C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>StoryID</t>
   </si>
@@ -254,6 +265,14 @@
     <t>res://Assets/Background/003/003_04.png</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>005_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -263,7 +282,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -277,7 +296,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -298,7 +317,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -386,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -432,9 +451,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -712,25 +734,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.1328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:14">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -750,28 +773,31 @@
         <v>17</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
         <v>34</v>
       </c>
@@ -785,36 +811,87 @@
         <v>25</v>
       </c>
       <c r="E2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="1" t="b">
+      <c r="K2" s="2"/>
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:14">
       <c r="C3" s="10"/>
-      <c r="K3" s="11"/>
-    </row>
-    <row r="4" spans="1:13" ht="18">
+      <c r="G3" s="17"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" ht="18">
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="C5" s="10"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="17"/>
+    </row>
+    <row r="18" spans="7:7">
+      <c r="G18" s="17"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="7:7">
+      <c r="G20" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -827,14 +904,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B2CC11-A98F-4F0D-965E-B7E42BA6168C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E374F2-C6D8-4833-8F38-85C0C42BB60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>StoryID</t>
   </si>
@@ -89,9 +89,6 @@
   <si>
     <t>TriggerType</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
   </si>
   <si>
     <t>TriggerDay</t>
@@ -240,9 +237,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>story_npc_cured</t>
-  </si>
-  <si>
     <t>005_02</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -270,7 +264,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>005_01</t>
+    <t>story_npc_cured</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerScene</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -737,20 +735,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -764,51 +761,51 @@
         <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -816,20 +813,18 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -949,22 +944,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -975,18 +970,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -997,18 +992,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E374F2-C6D8-4833-8F38-85C0C42BB60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57D7504-2459-4746-9607-F40FCF719A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>StoryID</t>
   </si>
@@ -270,6 +270,10 @@
   <si>
     <t>TriggerScene</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -350,7 +354,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,6 +376,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -403,7 +413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -450,6 +460,12 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -732,25 +748,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -763,38 +780,41 @@
       <c r="D1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
@@ -807,86 +827,87 @@
       <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1">
-        <v>0</v>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1" t="b">
+      <c r="L2" s="1"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="C3" s="10"/>
-      <c r="G3" s="17"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="H3" s="17"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="C4" s="10"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="C5" s="10"/>
-      <c r="G5" s="17"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="G6" s="17"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="G7" s="17"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="G8" s="17"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="G10" s="17"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="G11" s="17"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="G13" s="17"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="G16" s="17"/>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="17"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="17"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="17"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="17"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="H10" s="17"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57D7504-2459-4746-9607-F40FCF719A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E11C20-FE5F-4FA7-9AD1-2F27F9E086B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4305" yWindow="2850" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -89,15 +78,6 @@
   <si>
     <t>TriggerType</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
   </si>
   <si>
     <t>NpcID</t>
@@ -275,6 +255,25 @@
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerDay</t>
+  </si>
 </sst>
 </file>
 
@@ -284,7 +283,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -298,7 +297,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -319,7 +318,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -470,7 +469,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -748,26 +747,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -778,57 +780,63 @@
         <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="P1" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="18" t="s">
+      <c r="E2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -840,61 +848,63 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="1" t="b">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="8:8">
@@ -920,14 +930,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -965,22 +975,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -991,18 +1001,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1013,18 +1023,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E11C20-FE5F-4FA7-9AD1-2F27F9E086B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA35698C-3903-4565-92B2-428346AA168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="2850" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
   <si>
     <t>StoryID</t>
   </si>
@@ -63,10 +74,6 @@
   <si>
     <t>BackgroundPath</t>
     <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Hide</t>
@@ -181,6 +188,87 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>005_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>治愈世子</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>after</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_04.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>story_npc_cured</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerScene</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerDay</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>名声+1000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>草民行医只取诊费十文，这一千两小人不能收。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少掌柜的那可是一千两白银啊！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <t>先生真是</t>
     </r>
@@ -212,67 +300,24 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>无以为报</t>
+      <t>无以为报。这一千两白银是我的一点心意，感谢先生救命之恩。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>005_02</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>治愈世子</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>after</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>dim</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>res://Assets/Background/003/003_04.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>story_npc_cured</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
+    <t>世子乃人中龙凤，可天下人只要来看病，草民眼里看到的就只有病人。十文是诊费，绝非世子命价。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>……先生好风骨，本王平日见的那些儒生满口仁义，可见了真金白银没几个不迷糊的。有您这样的大夫是天下苍生之福啊。</t>
+    <rPh sb="2" eb="4">
+      <t>センセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>先生的恩情本王记下了，日后有能帮到先生的地方尽管开口。</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -283,7 +328,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -297,7 +342,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -318,7 +363,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -469,7 +514,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -748,25 +793,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -774,69 +819,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="K1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="O1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="18" t="s">
         <v>18</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="18" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -848,12 +893,18 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="N2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O2" s="2">
+        <v>5</v>
+      </c>
       <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
@@ -930,14 +981,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -958,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>10</v>
@@ -975,22 +1026,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1001,18 +1052,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1023,91 +1074,147 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="12" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="8"/>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="13" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="1"/>
+      <c r="H7" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="13" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="13" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA35698C-3903-4565-92B2-428346AA168D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF943628-E985-4392-ACA0-188947EC99BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -223,10 +223,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>TriggerCureCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Reputation</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -317,6 +313,10 @@
   </si>
   <si>
     <t>先生的恩情本王记下了，日后有能帮到先生的地方尽管开口。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>005_01</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -792,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -806,15 +806,14 @@
     <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -831,16 +830,16 @@
         <v>17</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>33</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
@@ -848,26 +847,23 @@
       <c r="K1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>36</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="19" t="s">
-        <v>38</v>
+      <c r="O1" s="18" t="s">
+        <v>16</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>27</v>
       </c>
@@ -889,73 +885,72 @@
       <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N2" s="2">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="O2" s="2">
-        <v>5</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="17"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="17"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="17"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16">
       <c r="H6" s="17"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16">
       <c r="H7" s="17"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16">
       <c r="H8" s="17"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16">
       <c r="H9" s="17"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16">
       <c r="H10" s="17"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16">
       <c r="H11" s="17"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16">
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16">
       <c r="H13" s="17"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16">
       <c r="H14" s="17"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16">
       <c r="H15" s="17"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16">
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="8:8">
@@ -1085,7 +1080,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1107,7 +1102,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1118,10 +1113,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
@@ -1129,7 +1124,7 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1151,7 +1146,7 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1173,7 +1168,7 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1195,7 +1190,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1203,7 +1198,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF943628-E985-4392-ACA0-188947EC99BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCC996-5675-4920-91F6-D33DCA9019E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
   <si>
     <t>StoryID</t>
   </si>
@@ -90,10 +79,6 @@
     <t>NpcID</t>
   </si>
   <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -107,10 +92,6 @@
   </si>
   <si>
     <t>night</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>shi_zi</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -319,6 +300,10 @@
     <t>005_01</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +313,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -342,7 +327,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -363,7 +348,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -514,7 +499,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -793,24 +778,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -824,60 +809,60 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>16</v>
-      </c>
       <c r="P1" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -886,13 +871,11 @@
         <v>0</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2">
         <v>1000</v>
@@ -976,14 +959,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1021,22 +1004,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1047,18 +1030,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1069,18 +1052,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1091,18 +1074,18 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1113,18 +1096,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1135,18 +1118,18 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1157,18 +1140,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1179,18 +1162,18 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1198,17 +1181,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCC996-5675-4920-91F6-D33DCA9019E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F6A76-8B93-4912-976B-2327E4977BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5317" yWindow="3863" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -864,12 +864,8 @@
       <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
         <v>49</v>
       </c>

--- a/DataTables/DetailText/剧情/005_02治愈世子.xlsx
+++ b/DataTables/DetailText/剧情/005_02治愈世子.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F6A76-8B93-4912-976B-2327E4977BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A476B80E-B073-431A-AD26-EF1553FD6D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -188,10 +199,6 @@
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
-    <t>res://Assets/Background/003/003_04.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>TriggerStoryID</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -303,6 +310,52 @@
   <si>
     <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_04.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -313,7 +366,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -327,7 +380,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -348,7 +401,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -499,7 +552,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -778,24 +831,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -809,37 +862,37 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>36</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>37</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>29</v>
       </c>
       <c r="M1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>34</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>35</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>15</v>
@@ -856,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -867,7 +920,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -955,14 +1008,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1012,7 +1065,7 @@
         <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>23</v>
@@ -1059,7 +1112,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1081,7 +1134,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1092,10 +1145,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
@@ -1103,7 +1156,7 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1125,7 +1178,7 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1147,7 +1200,7 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1169,7 +1222,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1177,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
@@ -1187,7 +1240,7 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
